--- a/CJFAS-Submission/Tables/Table2.xlsx
+++ b/CJFAS-Submission/Tables/Table2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rames\Documents\CHUMputerVisionProject\ManuscriptSubmission\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rames\Documents\GitHub\chumputer-manuscript\CJFAS-Submission\Tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FB86DC3E-AD15-47FD-BBED-0B659F9215C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6836A288-C6E5-4A82-BE42-E91E9ED83199}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30180" yWindow="5325" windowWidth="37755" windowHeight="16860" xr2:uid="{2068ED51-EF85-422D-A9BF-82A8376C1671}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2068ED51-EF85-422D-A9BF-82A8376C1671}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -86,16 +86,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
@@ -151,25 +143,34 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -509,21 +510,22 @@
   <dimension ref="A1:H14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="21.5703125" customWidth="1"/>
-    <col min="2" max="2" width="30.7109375" customWidth="1"/>
+    <col min="1" max="1" width="15.42578125" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="3" max="8" width="8.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="5"/>
-      <c r="B1" s="5"/>
-      <c r="C1" s="6" t="s">
+    <row r="1" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="8"/>
+      <c r="B1" s="8"/>
+      <c r="C1" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
-      <c r="H1" s="5"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="8"/>
     </row>
     <row r="2" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -551,7 +553,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>3</v>
       </c>
@@ -573,11 +575,11 @@
       <c r="G3" s="4">
         <v>4</v>
       </c>
-      <c r="H3" s="3">
+      <c r="H3" s="5">
         <v>52</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3"/>
       <c r="B4" s="1" t="s">
         <v>5</v>
@@ -597,11 +599,11 @@
       <c r="G4" s="4">
         <v>1</v>
       </c>
-      <c r="H4" s="3">
+      <c r="H4" s="5">
         <v>70</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3"/>
       <c r="B5" s="1" t="s">
         <v>6</v>
@@ -611,9 +613,9 @@
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
       <c r="G5" s="4"/>
-      <c r="H5" s="3"/>
-    </row>
-    <row r="6" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="H5" s="5"/>
+    </row>
+    <row r="6" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3"/>
       <c r="B6" s="1" t="s">
         <v>7</v>
@@ -633,11 +635,11 @@
       <c r="G6" s="4">
         <v>10</v>
       </c>
-      <c r="H6" s="3">
+      <c r="H6" s="5">
         <v>59</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3"/>
       <c r="B7" s="1" t="s">
         <v>8</v>
@@ -655,35 +657,35 @@
       <c r="G7" s="4">
         <v>1</v>
       </c>
-      <c r="H7" s="3">
+      <c r="H7" s="5">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3"/>
       <c r="B8" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C8" s="2">
+      <c r="C8" s="6">
         <v>14</v>
       </c>
-      <c r="D8" s="2">
+      <c r="D8" s="6">
         <v>34</v>
       </c>
-      <c r="E8" s="2">
+      <c r="E8" s="6">
         <v>54</v>
       </c>
-      <c r="F8" s="2">
+      <c r="F8" s="6">
         <v>68</v>
       </c>
-      <c r="G8" s="2">
+      <c r="G8" s="6">
         <v>16</v>
       </c>
-      <c r="H8" s="1">
+      <c r="H8" s="7">
         <v>186</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>9</v>
       </c>
@@ -705,11 +707,11 @@
       <c r="G9" s="4">
         <v>3</v>
       </c>
-      <c r="H9" s="3">
+      <c r="H9" s="5">
         <v>83</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3"/>
       <c r="B10" s="1" t="s">
         <v>5</v>
@@ -729,11 +731,11 @@
       <c r="G10" s="4">
         <v>2</v>
       </c>
-      <c r="H10" s="3">
+      <c r="H10" s="5">
         <v>69</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3"/>
       <c r="B11" s="1" t="s">
         <v>6</v>
@@ -745,11 +747,11 @@
         <v>1</v>
       </c>
       <c r="G11" s="4"/>
-      <c r="H11" s="3">
+      <c r="H11" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3"/>
       <c r="B12" s="1" t="s">
         <v>7</v>
@@ -769,11 +771,11 @@
       <c r="G12" s="4">
         <v>11</v>
       </c>
-      <c r="H12" s="3">
+      <c r="H12" s="5">
         <v>70</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3"/>
       <c r="B13" s="1" t="s">
         <v>8</v>
@@ -789,31 +791,31 @@
         <v>1</v>
       </c>
       <c r="G13" s="4"/>
-      <c r="H13" s="3">
+      <c r="H13" s="5">
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3"/>
       <c r="B14" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C14" s="2">
+      <c r="C14" s="6">
         <v>15</v>
       </c>
-      <c r="D14" s="2">
+      <c r="D14" s="6">
         <v>57</v>
       </c>
-      <c r="E14" s="2">
+      <c r="E14" s="6">
         <v>60</v>
       </c>
-      <c r="F14" s="2">
+      <c r="F14" s="6">
         <v>79</v>
       </c>
-      <c r="G14" s="2">
+      <c r="G14" s="6">
         <v>16</v>
       </c>
-      <c r="H14" s="1">
+      <c r="H14" s="7">
         <v>227</v>
       </c>
     </row>
